--- a/artfynd/A 33216-2023 artfynd.xlsx
+++ b/artfynd/A 33216-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33216-2023 artfynd.xlsx
+++ b/artfynd/A 33216-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -810,11 +810,11 @@
         <v>111590552</v>
       </c>
       <c r="B3" t="n">
-        <v>57508</v>
+        <v>56272</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -867,10 +867,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>539224.9058763792</v>
+        <v>539224</v>
       </c>
       <c r="R3" t="n">
-        <v>6658708.536939755</v>
+        <v>6658708</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1186,149 +1186,6 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>111460973</v>
-      </c>
-      <c r="B6" t="n">
-        <v>57752</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>206002</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Brunlångöra</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Plecotus auritus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>funnen död</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Älgsjöbo, Dlr</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>539179</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6658725</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Smedjebacken</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Söderbärke</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:05</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2023-08-07</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:05</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Halvt uppäten. Övre halva kroppen kvar.</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Nadja Odenhage</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Nadja Odenhage</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33216-2023 artfynd.xlsx
+++ b/artfynd/A 33216-2023 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>111590552</v>
       </c>
       <c r="B3" t="n">
-        <v>56272</v>
+        <v>56280</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 33216-2023 artfynd.xlsx
+++ b/artfynd/A 33216-2023 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>111590552</v>
       </c>
       <c r="B3" t="n">
-        <v>56280</v>
+        <v>56284</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 33216-2023 artfynd.xlsx
+++ b/artfynd/A 33216-2023 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>111590552</v>
       </c>
       <c r="B3" t="n">
-        <v>56287</v>
+        <v>56292</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
